--- a/data/B24_department_schedules_finals/Jeoloji Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/Jeoloji Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FACF6F7-F63F-487F-9BB7-01B81AFB9EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{1FACF6F7-F63F-487F-9BB7-01B81AFB9EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BA632FF-E689-4DF8-AF7B-C3D62647D82A}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
   <si>
     <t>Year:</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>YLAB 2</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -268,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -285,11 +288,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -368,15 +378,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}" name="Table1" displayName="Table1" ref="A1:F24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F24" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9AA74D43-5C0D-4306-BA2C-33CA0D410808}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{F7E028DF-0DCD-415A-98CA-91B412F89F36}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{8C05F5BE-9786-4856-B842-56932FB33F47}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{152198DF-19A4-4BC8-9C22-22E53A138922}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{F0A321C5-0531-4413-A331-945817A1B833}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{4F78AD98-4FF1-4478-9539-6BE250A65DF9}" name="Rooms Used" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}" name="Table1" displayName="Table1" ref="A1:G24" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G24" xr:uid="{5D0CA9D1-C38C-4145-8F6A-FEF06C22039D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{9AA74D43-5C0D-4306-BA2C-33CA0D410808}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{F7E028DF-0DCD-415A-98CA-91B412F89F36}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{8C05F5BE-9786-4856-B842-56932FB33F47}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{152198DF-19A4-4BC8-9C22-22E53A138922}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{F0A321C5-0531-4413-A331-945817A1B833}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{4F78AD98-4FF1-4478-9539-6BE250A65DF9}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{926C691F-784D-4402-86C1-98CA5B9B57C0}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -669,15 +680,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="33.265625" customWidth="1"/>
+    <col min="6" max="6" width="42.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,8 +707,11 @@
       <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -716,8 +730,12 @@
       <c r="F2" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -736,8 +754,12 @@
       <c r="F3" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -756,8 +778,12 @@
       <c r="F4" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -776,8 +802,12 @@
       <c r="F5" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>6</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -796,8 +826,11 @@
       <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -816,8 +849,12 @@
       <c r="F7" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -836,8 +873,12 @@
       <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -856,8 +897,12 @@
       <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -876,8 +921,12 @@
       <c r="F10" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -896,8 +945,11 @@
       <c r="F11" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -916,8 +968,11 @@
       <c r="F12" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -936,8 +991,11 @@
       <c r="F13" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -956,8 +1014,11 @@
       <c r="F14" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -976,8 +1037,11 @@
       <c r="F15" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -996,8 +1060,11 @@
       <c r="F16" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1016,8 +1083,11 @@
       <c r="F17" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1036,8 +1106,11 @@
       <c r="F18" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1056,8 +1129,11 @@
       <c r="F19" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="5">
         <v>4</v>
       </c>
@@ -1076,8 +1152,11 @@
       <c r="F20" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5">
         <v>4</v>
       </c>
@@ -1096,8 +1175,11 @@
       <c r="F21" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5">
         <v>4</v>
       </c>
@@ -1116,8 +1198,11 @@
       <c r="F22" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1136,8 +1221,11 @@
       <c r="F23" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1155,6 +1243,9 @@
       </c>
       <c r="F24" s="5" t="s">
         <v>52</v>
+      </c>
+      <c r="G24" s="7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
